--- a/Data.xlsx
+++ b/Data.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\source\repos\TP_3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\source\repos\Lab_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A39C04B-D588-4096-9D3E-9A0C7C14B312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D36427-23BB-49B9-BAB5-2E1D97AFD66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="InflationData" sheetId="1" r:id="rId1"/>
+    <sheet name="SheetData" sheetId="2" r:id="rId2"/>
+    <sheet name="MigrationData" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">InflationData!$A$2:$D$140</definedName>
@@ -23,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
   <si>
     <t>Ключевая ставка, % годовых</t>
   </si>
@@ -36,15 +38,28 @@
   <si>
     <t>Inflation</t>
   </si>
+  <si>
+    <t>Currency_USD</t>
+  </si>
+  <si>
+    <t>Currency_EUR</t>
+  </si>
+  <si>
+    <t>Immigrants</t>
+  </si>
+  <si>
+    <t>Emigrants</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-419]mmmm\ yyyy;@"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -60,6 +75,28 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.6"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -69,7 +106,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -77,14 +114,61 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2252,4 +2336,550 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE8F8FE6-F831-46C6-BCD0-9556235CB01C}">
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
+        <v>45748</v>
+      </c>
+      <c r="B2">
+        <v>90.1</v>
+      </c>
+      <c r="C2">
+        <v>96.88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>45749</v>
+      </c>
+      <c r="B3">
+        <v>90.07</v>
+      </c>
+      <c r="C3">
+        <v>97.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>45750</v>
+      </c>
+      <c r="B4">
+        <v>90.2</v>
+      </c>
+      <c r="C4">
+        <v>97.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>45751</v>
+      </c>
+      <c r="B5">
+        <v>90.51</v>
+      </c>
+      <c r="C5">
+        <v>97.04</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>45752</v>
+      </c>
+      <c r="B6">
+        <v>90.46</v>
+      </c>
+      <c r="C6">
+        <v>97.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>45753</v>
+      </c>
+      <c r="B7">
+        <v>90.41</v>
+      </c>
+      <c r="C7">
+        <v>96.96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>45754</v>
+      </c>
+      <c r="B8">
+        <v>90.73</v>
+      </c>
+      <c r="C8">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>45755</v>
+      </c>
+      <c r="B9">
+        <v>90.88</v>
+      </c>
+      <c r="C9">
+        <v>96.61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
+        <v>45756</v>
+      </c>
+      <c r="B10">
+        <v>90.79</v>
+      </c>
+      <c r="C10">
+        <v>96.34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>45757</v>
+      </c>
+      <c r="B11">
+        <v>90.9</v>
+      </c>
+      <c r="C11">
+        <v>96.38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
+        <v>45758</v>
+      </c>
+      <c r="B12">
+        <v>90.8</v>
+      </c>
+      <c r="C12">
+        <v>96.53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>45759</v>
+      </c>
+      <c r="B13">
+        <v>90.71</v>
+      </c>
+      <c r="C13">
+        <v>96.56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
+        <v>45760</v>
+      </c>
+      <c r="B14">
+        <v>90.76</v>
+      </c>
+      <c r="C14">
+        <v>96.54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>45761</v>
+      </c>
+      <c r="B15">
+        <v>90.38</v>
+      </c>
+      <c r="C15">
+        <v>96.48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>45762</v>
+      </c>
+      <c r="B16">
+        <v>90.03</v>
+      </c>
+      <c r="C16">
+        <v>96.18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>45763</v>
+      </c>
+      <c r="B17">
+        <v>89.92</v>
+      </c>
+      <c r="C17">
+        <v>96.04</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>45764</v>
+      </c>
+      <c r="B18">
+        <v>89.72</v>
+      </c>
+      <c r="C18">
+        <v>95.95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
+        <v>45765</v>
+      </c>
+      <c r="B19">
+        <v>89.78</v>
+      </c>
+      <c r="C19">
+        <v>96.16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="4">
+        <v>45766</v>
+      </c>
+      <c r="B20">
+        <v>89.6</v>
+      </c>
+      <c r="C20">
+        <v>96.23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>45767</v>
+      </c>
+      <c r="B21">
+        <v>89.31</v>
+      </c>
+      <c r="C21">
+        <v>95.87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="4">
+        <v>45768</v>
+      </c>
+      <c r="B22">
+        <v>89.61</v>
+      </c>
+      <c r="C22">
+        <v>95.94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="4">
+        <v>45769</v>
+      </c>
+      <c r="B23">
+        <v>89.56</v>
+      </c>
+      <c r="C23">
+        <v>95.86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="4">
+        <v>45770</v>
+      </c>
+      <c r="B24">
+        <v>89.58</v>
+      </c>
+      <c r="C24">
+        <v>95.73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="4">
+        <v>45771</v>
+      </c>
+      <c r="B25">
+        <v>89.29</v>
+      </c>
+      <c r="C25">
+        <v>95.85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="4">
+        <v>45772</v>
+      </c>
+      <c r="B26">
+        <v>89.18</v>
+      </c>
+      <c r="C26">
+        <v>96.06</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="4">
+        <v>45773</v>
+      </c>
+      <c r="B27">
+        <v>89.2</v>
+      </c>
+      <c r="C27">
+        <v>96.24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="4">
+        <v>45774</v>
+      </c>
+      <c r="B28">
+        <v>88.97</v>
+      </c>
+      <c r="C28">
+        <v>96.07</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="4">
+        <v>45775</v>
+      </c>
+      <c r="B29">
+        <v>89.05</v>
+      </c>
+      <c r="C29">
+        <v>96.01</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="4">
+        <v>45776</v>
+      </c>
+      <c r="B30">
+        <v>88.93</v>
+      </c>
+      <c r="C30">
+        <v>96.08</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="4">
+        <v>45777</v>
+      </c>
+      <c r="B31">
+        <v>88.87</v>
+      </c>
+      <c r="C31">
+        <v>96.27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57E11080-1F9B-40CA-81EA-56F91E205A5C}">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="7">
+        <v>40361</v>
+      </c>
+      <c r="B2" s="10">
+        <v>300</v>
+      </c>
+      <c r="C2" s="10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="7">
+        <v>40727</v>
+      </c>
+      <c r="B3" s="10">
+        <v>320</v>
+      </c>
+      <c r="C3" s="10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7">
+        <v>41093</v>
+      </c>
+      <c r="B4" s="10">
+        <v>350</v>
+      </c>
+      <c r="C4" s="10">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7">
+        <v>41459</v>
+      </c>
+      <c r="B5" s="10">
+        <v>400</v>
+      </c>
+      <c r="C5" s="10">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="7">
+        <v>41825</v>
+      </c>
+      <c r="B6" s="10">
+        <v>450</v>
+      </c>
+      <c r="C6" s="10">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="7">
+        <v>42191</v>
+      </c>
+      <c r="B7" s="10">
+        <v>500</v>
+      </c>
+      <c r="C7" s="10">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="7">
+        <v>42557</v>
+      </c>
+      <c r="B8" s="10">
+        <v>480</v>
+      </c>
+      <c r="C8" s="10">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="7">
+        <v>42923</v>
+      </c>
+      <c r="B9" s="10">
+        <v>460</v>
+      </c>
+      <c r="C9" s="10">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="7">
+        <v>43289</v>
+      </c>
+      <c r="B10" s="10">
+        <v>430</v>
+      </c>
+      <c r="C10" s="10">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="7">
+        <v>43655</v>
+      </c>
+      <c r="B11" s="10">
+        <v>410</v>
+      </c>
+      <c r="C11" s="10">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
+        <v>44021</v>
+      </c>
+      <c r="B12" s="10">
+        <v>390</v>
+      </c>
+      <c r="C12" s="10">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
+        <v>44387</v>
+      </c>
+      <c r="B13" s="10">
+        <v>370</v>
+      </c>
+      <c r="C13" s="10">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="7">
+        <v>44753</v>
+      </c>
+      <c r="B14" s="10">
+        <v>350</v>
+      </c>
+      <c r="C14" s="10">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="7">
+        <v>45119</v>
+      </c>
+      <c r="B15" s="10">
+        <v>340</v>
+      </c>
+      <c r="C15" s="10">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="7">
+        <v>45485</v>
+      </c>
+      <c r="B16" s="11">
+        <v>330</v>
+      </c>
+      <c r="C16" s="11">
+        <v>220</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>